--- a/output/pdf_financials_xlsx/DIAM.xlsx
+++ b/output/pdf_financials_xlsx/DIAM.xlsx
@@ -6011,10 +6011,10 @@
         <v>35.31</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>35.504</v>
+        <v>37.719</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>37.229</v>
+        <v>38.914</v>
       </c>
     </row>
     <row r="93">
@@ -10357,7 +10357,11 @@
           <t>Warrant reserve (note 20)</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/DIAM.xlsx
+++ b/output/pdf_financials_xlsx/DIAM.xlsx
@@ -7877,13 +7877,13 @@
         <v>0</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="R124" s="3" t="n">
-        <v>0</v>
+        <v>-0.114</v>
       </c>
     </row>
     <row r="125">
@@ -7935,13 +7935,13 @@
         <v>0</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="R125" s="3" t="n">
-        <v>0</v>
+        <v>-0.114</v>
       </c>
     </row>
     <row r="126">
@@ -22082,7 +22082,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
           <t>-</t>
@@ -24848,7 +24852,11 @@
           <t>Lease payments (note 14)</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr"/>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E167" t="inlineStr">
         <is>
           <t>-</t>
@@ -32456,7 +32464,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">

--- a/output/pdf_financials_xlsx/DIAM.xlsx
+++ b/output/pdf_financials_xlsx/DIAM.xlsx
@@ -2064,28 +2064,28 @@
         <v>0</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>0.079</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0</v>
+        <v>0.126</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0</v>
+        <v>0.108</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0</v>
+        <v>0.096</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0</v>
+        <v>0.098</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0</v>
+        <v>0.091</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>0</v>
+        <v>0.709</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>0</v>
+        <v>1.004</v>
       </c>
     </row>
     <row r="29">
@@ -2122,28 +2122,28 @@
         <v>-5.384</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>40.75</v>
+        <v>40.829</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-4.581</v>
+        <v>-4.455</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-4.117</v>
+        <v>-4.009</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-7.689</v>
+        <v>-7.593</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-68.788</v>
+        <v>-68.69</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-2.823</v>
+        <v>-2.732</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-6.017</v>
+        <v>-5.308</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-3.819</v>
+        <v>-2.815</v>
       </c>
     </row>
     <row r="30">
@@ -6440,28 +6440,28 @@
         <v>0</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.079</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.126</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.108</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>0.096</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>0.098</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>0.091</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>0.709</v>
       </c>
       <c r="R100" s="3" t="n">
-        <v>0</v>
+        <v>1.004</v>
       </c>
     </row>
     <row r="101">
@@ -7121,16 +7121,16 @@
         <v>0</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.138</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>0.664</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>0.157</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>0.073</v>
       </c>
       <c r="J112" s="3" t="n">
         <v>0</v>
@@ -7139,7 +7139,7 @@
         <v>0</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="M112" s="3" t="n">
         <v>0</v>
@@ -7154,10 +7154,10 @@
         <v>0</v>
       </c>
       <c r="Q112" s="3" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="R112" s="3" t="n">
-        <v>0</v>
+        <v>0.064</v>
       </c>
     </row>
     <row r="113">
@@ -7603,25 +7603,25 @@
         </is>
       </c>
       <c r="B120" s="3" t="n">
-        <v>0</v>
+        <v>12.167</v>
       </c>
       <c r="C120" s="3" t="n">
-        <v>0</v>
+        <v>25.837</v>
       </c>
       <c r="D120" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E120" s="3" t="n">
-        <v>0</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="G120" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H120" s="3" t="n">
-        <v>0</v>
+        <v>4.981</v>
       </c>
       <c r="I120" s="3" t="n">
         <v>0</v>
@@ -19963,7 +19963,11 @@
           <t>Depreciation on property, plant and equipment (note 11)</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
           <t>-</t>
@@ -21680,7 +21684,11 @@
           <t>Proceeds from sale of property and equipment</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
           <t>-</t>
@@ -23317,7 +23325,11 @@
           <t>Depreciation on property and equipment</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
           <t>-</t>
@@ -24468,7 +24480,11 @@
           <t>Proceeds from disposal of property and equipment (note 11)</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr"/>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E163" t="inlineStr">
         <is>
           <t>-</t>
@@ -27292,7 +27308,11 @@
           <t>Proceeds from disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr"/>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E193" t="inlineStr">
         <is>
           <t>-</t>
@@ -28634,7 +28654,11 @@
           <t>Issue of common shares (net of issue costs)</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E207" s="5" t="n">
         <v>12.167</v>
       </c>
@@ -28927,7 +28951,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr"/>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E210" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/DIAM.xlsx
+++ b/output/pdf_financials_xlsx/DIAM.xlsx
@@ -4236,10 +4236,10 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>10.705</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.762</v>
       </c>
       <c r="D64" s="3" t="n">
         <v>0</v>
@@ -4413,10 +4413,10 @@
         <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>1.301</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="E67" s="3" t="n">
         <v>0</v>
@@ -4452,13 +4452,13 @@
         <v>0</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.469</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>0.305</v>
       </c>
       <c r="R67" s="3" t="n">
-        <v>0</v>
+        <v>0.165</v>
       </c>
     </row>
     <row r="68">
@@ -4468,7 +4468,7 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>0</v>
+        <v>10.705</v>
       </c>
       <c r="C68" s="3" t="n">
         <v>2.063</v>
@@ -6916,13 +6916,13 @@
         <v>0</v>
       </c>
       <c r="O108" s="3" t="n">
-        <v>0</v>
+        <v>66.34399999999999</v>
       </c>
       <c r="P108" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q108" s="3" t="n">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="R108" s="3" t="n">
         <v>0</v>
@@ -20866,7 +20866,11 @@
           <t>Impairment charge (note 12)</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E125" t="inlineStr">
         <is>
           <t>-</t>
@@ -23610,7 +23614,11 @@
           <t>Impairment charge (note 12)</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
           <t>-</t>
@@ -25390,7 +25398,11 @@
           <t>Impairment charge</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr"/>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
           <t>-</t>
@@ -27405,7 +27417,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr"/>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E194" t="inlineStr">
         <is>
           <t>-</t>
@@ -31119,7 +31135,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr"/>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E232" s="5" t="n">
         <v>-112.002</v>
       </c>
